--- a/templates/BNY11585 - template.xlsx
+++ b/templates/BNY11585 - template.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20355" yWindow="-11640" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$6:$H$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$6:$H$46</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col width="13.42578125" customWidth="1" style="55" min="1" max="1"/>
@@ -1238,8 +1238,8 @@
     <col width="5.42578125" customWidth="1" style="55" min="9" max="9"/>
     <col width="23.140625" bestFit="1" customWidth="1" style="55" min="10" max="10"/>
     <col width="23.42578125" bestFit="1" customWidth="1" style="55" min="11" max="11"/>
-    <col width="9.140625" customWidth="1" style="55" min="12" max="22"/>
-    <col width="9.140625" customWidth="1" style="55" min="23" max="16384"/>
+    <col width="9.140625" customWidth="1" style="55" min="12" max="23"/>
+    <col width="9.140625" customWidth="1" style="55" min="24" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1392,14 +1392,14 @@
     <row r="21" ht="15.95" customFormat="1" customHeight="1" s="28">
       <c r="B21" s="29" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C21" s="30" t="n">
-        <v>1.59790292</v>
+        <v>1.60390707</v>
       </c>
       <c r="D21" s="31" t="n">
-        <v>-3.152783000603954e-05</v>
+        <v>0.0001004647899500721</v>
       </c>
       <c r="E21" s="31" t="n">
         <v>0.0005426623598601132</v>
@@ -1408,23 +1408,23 @@
         <v>0.0006017779632476739</v>
       </c>
       <c r="G21" s="32" t="n">
-        <v>-0.05809842793254859</v>
+        <v>0.1851331460983766</v>
       </c>
       <c r="H21" s="32" t="n">
-        <v>-0.05239113415833677</v>
+        <v>0.16694660836014</v>
       </c>
     </row>
     <row r="22" ht="15.95" customFormat="1" customHeight="1" s="28">
       <c r="B22" s="33" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C22" s="34" t="n">
-        <v>1.5979533</v>
+        <v>1.60374595</v>
       </c>
       <c r="D22" s="35" t="n">
-        <v>-0.002425880246142431</v>
+        <v>0.0005464135796604541</v>
       </c>
       <c r="E22" s="35" t="n">
         <v>0.0005426623598601132</v>
@@ -1433,23 +1433,23 @@
         <v>0.0006017779632476739</v>
       </c>
       <c r="G22" s="36" t="n">
-        <v>-4.470330772098826</v>
+        <v>1.006912622060811</v>
       </c>
       <c r="H22" s="36" t="n">
-        <v>-4.031188236023876</v>
+        <v>0.9079986523793105</v>
       </c>
     </row>
     <row r="23" ht="15.95" customFormat="1" customHeight="1" s="28">
       <c r="B23" s="33" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C23" s="34" t="n">
-        <v>1.60183917</v>
+        <v>1.60287012</v>
       </c>
       <c r="D23" s="35" t="n">
-        <v>0.0001900739263380746</v>
+        <v>0.0008499046889520745</v>
       </c>
       <c r="E23" s="35" t="n">
         <v>0.0005426623598601132</v>
@@ -1458,23 +1458,23 @@
         <v>0.0006017779632476739</v>
       </c>
       <c r="G23" s="36" t="n">
-        <v>0.3502618578282666</v>
+        <v>1.566175861489936</v>
       </c>
       <c r="H23" s="36" t="n">
-        <v>0.315853916139242</v>
+        <v>1.412322718441385</v>
       </c>
     </row>
     <row r="24" ht="15.95" customFormat="1" customHeight="1" s="28">
       <c r="B24" s="33" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C24" s="34" t="n">
-        <v>1.60153476</v>
+        <v>1.60150899</v>
       </c>
       <c r="D24" s="35" t="n">
-        <v>0.0004710326537287202</v>
+        <v>-0.001242418769362819</v>
       </c>
       <c r="E24" s="35" t="n">
         <v>0.0005426623598601132</v>
@@ -1483,23 +1483,23 @@
         <v>0.0006017779632476739</v>
       </c>
       <c r="G24" s="36" t="n">
-        <v>0.8680031794542417</v>
+        <v>-2.289487646946966</v>
       </c>
       <c r="H24" s="36" t="n">
-        <v>0.7827349662102153</v>
+        <v>-2.06458003655989</v>
       </c>
     </row>
     <row r="25" ht="15.95" customFormat="1" customHeight="1" s="28">
       <c r="B25" s="33" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C25" s="34" t="n">
-        <v>1.60078074</v>
+        <v>1.60350121</v>
       </c>
       <c r="D25" s="35" t="n">
-        <v>0.0005845564316164786</v>
+        <v>0.001727355233061223</v>
       </c>
       <c r="E25" s="35" t="n">
         <v>0.0005426623598601132</v>
@@ -1508,10 +1508,10 @@
         <v>0.0006017779632476739</v>
       </c>
       <c r="G25" s="36" t="n">
-        <v>1.077200990625487</v>
+        <v>3.183112301185765</v>
       </c>
       <c r="H25" s="36" t="n">
-        <v>0.971382249462486</v>
+        <v>2.870419554313748</v>
       </c>
     </row>
     <row r="26" ht="15.95" customHeight="1">
@@ -1563,24 +1563,24 @@
     <row r="28" ht="15.95" customFormat="1" customHeight="1" s="28">
       <c r="B28" s="37" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C28" s="37" t="inlineStr"/>
       <c r="D28" s="31" t="n">
-        <v>0.002312503029309632</v>
+        <v>0.002832785363505286</v>
       </c>
       <c r="E28" s="31" t="n">
-        <v>0.01048336746569301</v>
+        <v>0.003804826246388782</v>
       </c>
       <c r="F28" s="31" t="n">
-        <v>0.01161832663695161</v>
+        <v>0.004220058245789859</v>
       </c>
       <c r="G28" s="32" t="n">
-        <v>0.2205878060534782</v>
+        <v>0.7445242384442458</v>
       </c>
       <c r="H28" s="32" t="n">
-        <v>0.1990392507949303</v>
+        <v>0.6712668874491042</v>
       </c>
       <c r="I28" s="38" t="n"/>
     </row>
@@ -1592,19 +1592,19 @@
       </c>
       <c r="C29" s="39" t="inlineStr"/>
       <c r="D29" s="35" t="n">
-        <v>0.005231705925163421</v>
+        <v>0.003075122459491597</v>
       </c>
       <c r="E29" s="35" t="n">
-        <v>0.01159785506263344</v>
+        <v>0.0115104208368324</v>
       </c>
       <c r="F29" s="35" t="n">
-        <v>0.01285374137368023</v>
+        <v>0.01276619859936212</v>
       </c>
       <c r="G29" s="36" t="n">
-        <v>0.4510925422769936</v>
+        <v>0.2671598634909557</v>
       </c>
       <c r="H29" s="36" t="n">
-        <v>0.407018141494277</v>
+        <v>0.2408800423679175</v>
       </c>
       <c r="I29" s="40" t="n"/>
       <c r="J29" s="41" t="n"/>
@@ -1617,19 +1617,19 @@
       </c>
       <c r="C30" s="39" t="inlineStr"/>
       <c r="D30" s="35" t="n">
-        <v>0.02870383611451</v>
+        <v>0.02830456917386015</v>
       </c>
       <c r="E30" s="35" t="n">
-        <v>0.03528813776398843</v>
+        <v>0.03519865594435645</v>
       </c>
       <c r="F30" s="35" t="n">
-        <v>0.03914881930625902</v>
+        <v>0.03905900380096416</v>
       </c>
       <c r="G30" s="36" t="n">
-        <v>0.8134131731882515</v>
+        <v>0.8041377835166557</v>
       </c>
       <c r="H30" s="36" t="n">
-        <v>0.7331980024726031</v>
+        <v>0.7246618300378018</v>
       </c>
       <c r="I30" s="40" t="n"/>
     </row>
@@ -1641,19 +1641,19 @@
       </c>
       <c r="C31" s="39" t="inlineStr"/>
       <c r="D31" s="35" t="n">
-        <v>0.06525050407476396</v>
+        <v>0.06488726751662788</v>
       </c>
       <c r="E31" s="35" t="n">
-        <v>0.07186785093087189</v>
+        <v>0.07177520746070365</v>
       </c>
       <c r="F31" s="35" t="n">
-        <v>0.07987693752901182</v>
+        <v>0.07978360181905497</v>
       </c>
       <c r="G31" s="36" t="n">
-        <v>0.9079234070534123</v>
+        <v>0.9040345519328959</v>
       </c>
       <c r="H31" s="36" t="n">
-        <v>0.816887903984358</v>
+        <v>0.8132907770169213</v>
       </c>
       <c r="I31" s="40" t="n"/>
     </row>
@@ -1666,44 +1666,44 @@
       </c>
       <c r="C32" s="39" t="inlineStr"/>
       <c r="D32" s="35" t="n">
-        <v>0.1435466290680805</v>
+        <v>0.1403478716132505</v>
       </c>
       <c r="E32" s="35" t="n">
-        <v>0.1478169439809287</v>
+        <v>0.148016036262707</v>
       </c>
       <c r="F32" s="35" t="n">
-        <v>0.1650341981406351</v>
+        <v>0.1652362768066389</v>
       </c>
       <c r="G32" s="36" t="n">
-        <v>0.9711107888051103</v>
+        <v>0.9481936900685096</v>
       </c>
       <c r="H32" s="36" t="n">
-        <v>0.8697992942393438</v>
+        <v>0.8493768700530994</v>
       </c>
       <c r="I32" s="40" t="n"/>
     </row>
     <row r="33" ht="15.95" customFormat="1" customHeight="1" s="28">
-      <c r="A33" s="47" t="n"/>
+      <c r="A33" s="42" t="n"/>
       <c r="B33" s="39" t="inlineStr">
         <is>
-          <t>Ano 2026</t>
+          <t>Últimos 720 dias</t>
         </is>
       </c>
       <c r="C33" s="39" t="inlineStr"/>
       <c r="D33" s="35" t="n">
-        <v>0.02632222339255175</v>
+        <v>0.2633659953107343</v>
       </c>
       <c r="E33" s="35" t="n">
-        <v>0.03243902489712824</v>
+        <v>0.2779304689804314</v>
       </c>
       <c r="F33" s="35" t="n">
-        <v>0.03598299795768156</v>
+        <v>0.3165559174053354</v>
       </c>
       <c r="G33" s="36" t="n">
-        <v>0.8114369490459621</v>
+        <v>0.9475967002713815</v>
       </c>
       <c r="H33" s="36" t="n">
-        <v>0.7315183527372694</v>
+        <v>0.8319730601450303</v>
       </c>
       <c r="I33" s="40" t="n"/>
     </row>
@@ -1711,24 +1711,24 @@
       <c r="A34" s="47" t="n"/>
       <c r="B34" s="39" t="inlineStr">
         <is>
-          <t>Ano 2025</t>
+          <t>Ano 2026</t>
         </is>
       </c>
       <c r="C34" s="39" t="inlineStr"/>
       <c r="D34" s="35" t="n">
-        <v>0.145675618978681</v>
+        <v>0.03017864827322136</v>
       </c>
       <c r="E34" s="35" t="n">
-        <v>0.143132751155109</v>
+        <v>0.0380553842733744</v>
       </c>
       <c r="F34" s="35" t="n">
-        <v>0.1602797424224323</v>
+        <v>0.04223422499971918</v>
       </c>
       <c r="G34" s="36" t="n">
-        <v>1.017765799951797</v>
+        <v>0.7930191443195063</v>
       </c>
       <c r="H34" s="36" t="n">
-        <v>0.9088835356045136</v>
+        <v>0.7145543282355015</v>
       </c>
       <c r="I34" s="40" t="n"/>
     </row>
@@ -1736,155 +1736,169 @@
       <c r="A35" s="47" t="n"/>
       <c r="B35" s="39" t="inlineStr">
         <is>
-          <t>Ano 2024</t>
+          <t>Ano 2025</t>
         </is>
       </c>
       <c r="C35" s="39" t="inlineStr"/>
       <c r="D35" s="35" t="n">
-        <v>0.1126230753384481</v>
+        <v>0.145675618978681</v>
       </c>
       <c r="E35" s="35" t="n">
-        <v>0.1092049264357533</v>
+        <v>0.143132751155109</v>
       </c>
       <c r="F35" s="35" t="n">
-        <v>0.1259760418445097</v>
+        <v>0.1602797424224323</v>
       </c>
       <c r="G35" s="36" t="n">
-        <v>1.03130031779936</v>
+        <v>1.017765799951797</v>
       </c>
       <c r="H35" s="36" t="n">
-        <v>0.8940039208205715</v>
+        <v>0.9088835356045136</v>
       </c>
       <c r="I35" s="40" t="n"/>
     </row>
     <row r="36" ht="15.95" customFormat="1" customHeight="1" s="28">
-      <c r="A36" s="43" t="n"/>
+      <c r="A36" s="47" t="n"/>
       <c r="B36" s="39" t="inlineStr">
         <is>
-          <t>Acumulado²</t>
+          <t>Ano 2024</t>
         </is>
       </c>
       <c r="C36" s="39" t="inlineStr"/>
       <c r="D36" s="35" t="n">
-        <v>0.5979029199999999</v>
+        <v>0.1126230753384481</v>
       </c>
       <c r="E36" s="35" t="n">
-        <v>0.6485414412954158</v>
+        <v>0.1092049264357533</v>
       </c>
       <c r="F36" s="35" t="n">
-        <v>0.7529093752288043</v>
+        <v>0.1259760418445097</v>
       </c>
       <c r="G36" s="36" t="n">
-        <v>0.9219193746597457</v>
+        <v>1.03130031779936</v>
       </c>
       <c r="H36" s="36" t="n">
-        <v>0.7941233562383269</v>
+        <v>0.8940039208205715</v>
       </c>
       <c r="I36" s="40" t="n"/>
     </row>
-    <row r="37" ht="15.95" customHeight="1">
-      <c r="A37" s="3" t="n"/>
-      <c r="B37" s="10" t="n"/>
-      <c r="C37" s="7" t="n"/>
-      <c r="D37" s="7" t="n"/>
-      <c r="E37" s="7" t="n"/>
-      <c r="F37" s="7" t="n"/>
-      <c r="G37" s="7" t="n"/>
-      <c r="H37" s="7" t="n"/>
-      <c r="I37" s="3" t="n"/>
-    </row>
-    <row r="38" ht="26.1" customHeight="1">
-      <c r="B38" s="26" t="inlineStr">
+    <row r="37" ht="15.95" customFormat="1" customHeight="1" s="28">
+      <c r="A37" s="43" t="n"/>
+      <c r="B37" s="39" t="inlineStr">
+        <is>
+          <t>Acumulado²</t>
+        </is>
+      </c>
+      <c r="C37" s="39" t="inlineStr"/>
+      <c r="D37" s="35" t="n">
+        <v>0.60390707</v>
+      </c>
+      <c r="E37" s="35" t="n">
+        <v>0.6575093328199275</v>
+      </c>
+      <c r="F37" s="35" t="n">
+        <v>0.7634866091315553</v>
+      </c>
+      <c r="G37" s="36" t="n">
+        <v>0.9184768030743563</v>
+      </c>
+      <c r="H37" s="36" t="n">
+        <v>0.7909858048288855</v>
+      </c>
+      <c r="I37" s="40" t="n"/>
+    </row>
+    <row r="38" ht="15.95" customHeight="1">
+      <c r="A38" s="3" t="n"/>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="7" t="n"/>
+      <c r="D38" s="7" t="n"/>
+      <c r="E38" s="7" t="n"/>
+      <c r="F38" s="7" t="n"/>
+      <c r="G38" s="7" t="n"/>
+      <c r="H38" s="7" t="n"/>
+      <c r="I38" s="3" t="n"/>
+    </row>
+    <row r="39" ht="26.1" customHeight="1">
+      <c r="B39" s="26" t="inlineStr">
         <is>
           <t>Patrimônio Líquido (R$)</t>
         </is>
       </c>
-      <c r="C38" s="26" t="n"/>
-      <c r="D38" s="26" t="n"/>
-      <c r="E38" s="26" t="n"/>
-      <c r="F38" s="26" t="n"/>
-      <c r="G38" s="26" t="n"/>
-      <c r="H38" s="26" t="n"/>
-      <c r="I38" s="3" t="n"/>
-    </row>
-    <row r="39" ht="15.95" customHeight="1">
-      <c r="B39" s="11" t="inlineStr">
+      <c r="C39" s="26" t="n"/>
+      <c r="D39" s="26" t="n"/>
+      <c r="E39" s="26" t="n"/>
+      <c r="F39" s="26" t="n"/>
+      <c r="G39" s="26" t="n"/>
+      <c r="H39" s="26" t="n"/>
+      <c r="I39" s="3" t="n"/>
+    </row>
+    <row r="40" ht="15.95" customHeight="1">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>Hoje¹</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="n"/>
-      <c r="D39" s="12" t="n"/>
-      <c r="E39" s="54" t="n">
-        <v>47937087.52</v>
-      </c>
-      <c r="I39" s="3" t="n"/>
-    </row>
-    <row r="40" ht="15.95" customHeight="1">
-      <c r="B40" s="13" t="inlineStr">
-        <is>
-          <t>Últimos 12 Meses (Média Diária)¹</t>
         </is>
       </c>
       <c r="C40" s="12" t="n"/>
       <c r="D40" s="12" t="n"/>
       <c r="E40" s="54" t="n">
-        <v>44989020.9081746</v>
+        <v>48117212.12</v>
       </c>
       <c r="I40" s="3" t="n"/>
     </row>
     <row r="41" ht="15.95" customHeight="1">
-      <c r="B41" s="14" t="n"/>
-      <c r="C41" s="3" t="n"/>
-      <c r="D41" s="3" t="n"/>
-      <c r="E41" s="3" t="n"/>
-      <c r="F41" s="3" t="n"/>
-      <c r="G41" s="3" t="n"/>
-      <c r="H41" s="3" t="n"/>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>Últimos 12 Meses (Média Diária)¹</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="n"/>
+      <c r="D41" s="12" t="n"/>
+      <c r="E41" s="54" t="n">
+        <v>45225182.29138889</v>
+      </c>
       <c r="I41" s="3" t="n"/>
     </row>
     <row r="42" ht="15.95" customHeight="1">
-      <c r="A42" s="3" t="n"/>
-      <c r="B42" s="15" t="inlineStr">
-        <is>
-          <t>¹Data de Referência:</t>
-        </is>
-      </c>
-      <c r="C42" s="24" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="D42" s="17" t="n"/>
-      <c r="E42" s="17" t="n"/>
-      <c r="F42" s="17" t="n"/>
-      <c r="G42" s="17" t="n"/>
-      <c r="H42" s="17" t="n"/>
+      <c r="B42" s="14" t="n"/>
+      <c r="C42" s="3" t="n"/>
+      <c r="D42" s="3" t="n"/>
+      <c r="E42" s="3" t="n"/>
+      <c r="F42" s="3" t="n"/>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
       <c r="I42" s="3" t="n"/>
     </row>
     <row r="43" ht="15.95" customHeight="1">
       <c r="A43" s="3" t="n"/>
-      <c r="B43" s="18" t="inlineStr">
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>¹Data de Referência:</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D43" s="17" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="17" t="n"/>
+      <c r="G43" s="17" t="n"/>
+      <c r="H43" s="17" t="n"/>
+      <c r="I43" s="3" t="n"/>
+    </row>
+    <row r="44" ht="15.95" customHeight="1">
+      <c r="A44" s="3" t="n"/>
+      <c r="B44" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">²Cota Inicial em: </t>
         </is>
       </c>
-      <c r="C43" s="24" t="inlineStr">
+      <c r="C44" s="24" t="inlineStr">
         <is>
           <t>2022-02-04</t>
         </is>
       </c>
-      <c r="D43" s="19" t="n"/>
-      <c r="E43" s="19" t="n"/>
-      <c r="F43" s="19" t="n"/>
-      <c r="G43" s="19" t="n"/>
-      <c r="H43" s="19" t="n"/>
-      <c r="I43" s="3" t="n"/>
-    </row>
-    <row r="44" ht="10.5" customHeight="1">
-      <c r="A44" s="3" t="n"/>
-      <c r="B44" s="18" t="n"/>
-      <c r="C44" s="16" t="n"/>
       <c r="D44" s="19" t="n"/>
       <c r="E44" s="19" t="n"/>
       <c r="F44" s="19" t="n"/>
@@ -1892,49 +1906,50 @@
       <c r="H44" s="19" t="n"/>
       <c r="I44" s="3" t="n"/>
     </row>
-    <row r="45" ht="43.5" customHeight="1">
+    <row r="45" ht="10.5" customHeight="1">
       <c r="A45" s="3" t="n"/>
-      <c r="B45" s="25" t="inlineStr">
+      <c r="B45" s="18" t="n"/>
+      <c r="C45" s="16" t="n"/>
+      <c r="D45" s="19" t="n"/>
+      <c r="E45" s="19" t="n"/>
+      <c r="F45" s="19" t="n"/>
+      <c r="G45" s="19" t="n"/>
+      <c r="H45" s="19" t="n"/>
+      <c r="I45" s="3" t="n"/>
+    </row>
+    <row r="46" ht="43.5" customHeight="1">
+      <c r="A46" s="3" t="n"/>
+      <c r="B46" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">As informações contidas neste material são de caráter exclusivamente informativo. Fundos de investimento não contam com garantia do administrador do fundo, do gestor da carteira, de qualquer mecanismo de seguro ou, ainda, do Fundo Garantidor de Créditos – FGC. Rentabilidade passada não representa garantia de rentabilidade futura. "A rentabilidade divulgada não é líquida de impostos.“ Leia o prospecto e o regulamento antes de investir. </t>
         </is>
       </c>
-      <c r="C45" s="25" t="n"/>
-      <c r="D45" s="25" t="n"/>
-      <c r="E45" s="25" t="n"/>
-      <c r="F45" s="25" t="n"/>
-      <c r="G45" s="25" t="n"/>
-      <c r="H45" s="25" t="n"/>
-      <c r="I45" s="3" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="n"/>
-      <c r="B46" s="53" t="n"/>
+      <c r="C46" s="25" t="n"/>
+      <c r="D46" s="25" t="n"/>
+      <c r="E46" s="25" t="n"/>
+      <c r="F46" s="25" t="n"/>
+      <c r="G46" s="25" t="n"/>
+      <c r="H46" s="25" t="n"/>
       <c r="I46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n"/>
-      <c r="B47" s="20" t="n"/>
-      <c r="C47" s="20" t="n"/>
-      <c r="D47" s="20" t="n"/>
-      <c r="E47" s="20" t="n"/>
-      <c r="F47" s="20" t="n"/>
-      <c r="G47" s="20" t="n"/>
-      <c r="H47" s="20" t="n"/>
+      <c r="B47" s="53" t="n"/>
       <c r="I47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n"/>
-      <c r="B48" s="21" t="n"/>
-      <c r="C48" s="22" t="n"/>
-      <c r="D48" s="9" t="n"/>
-      <c r="E48" s="9" t="n"/>
-      <c r="F48" s="9" t="n"/>
-      <c r="G48" s="9" t="n"/>
-      <c r="H48" s="9" t="n"/>
+      <c r="B48" s="20" t="n"/>
+      <c r="C48" s="20" t="n"/>
+      <c r="D48" s="20" t="n"/>
+      <c r="E48" s="20" t="n"/>
+      <c r="F48" s="20" t="n"/>
+      <c r="G48" s="20" t="n"/>
+      <c r="H48" s="20" t="n"/>
       <c r="I48" s="3" t="n"/>
     </row>
     <row r="49">
+      <c r="A49" s="3" t="n"/>
       <c r="B49" s="21" t="n"/>
       <c r="C49" s="22" t="n"/>
       <c r="D49" s="9" t="n"/>
@@ -1942,14 +1957,24 @@
       <c r="F49" s="9" t="n"/>
       <c r="G49" s="9" t="n"/>
       <c r="H49" s="9" t="n"/>
+      <c r="I49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="21" t="n"/>
+      <c r="C50" s="22" t="n"/>
+      <c r="D50" s="9" t="n"/>
+      <c r="E50" s="9" t="n"/>
+      <c r="F50" s="9" t="n"/>
+      <c r="G50" s="9" t="n"/>
+      <c r="H50" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="E40:H40"/>
-    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="E41:H41"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="75"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="73"/>
 </worksheet>
 </file>